--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
@@ -536,7 +536,7 @@
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>

--- a/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Fabio Villa - CR ZANCANARO SANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
